--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6121-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6121-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6E7EC9E-027B-4C1F-A400-46B94EBAF48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98B3748B-EB9C-4D74-B903-F1E7AF41FCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{B55CBFDB-13AF-4714-9180-884D839166F2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E0806EE8-615D-461D-8291-14F9031E78A1}"/>
   </bookViews>
   <sheets>
     <sheet name="6121-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1472,25 +1472,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A92034-8C22-4F79-ADCC-2BAC1302B6E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65B0718-EB39-4E8C-A7E1-A6C9AFB49C75}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1644,7 +1644,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2023</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="41">
         <v>2022</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2021</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>2020</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2019</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2018</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2017</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <v>2016</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2015</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>2014</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2013</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2012</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2011</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>2010</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2009</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>2008</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2007</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>2006</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2005</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <v>2004</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2003</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>2002</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2001</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>2000</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>1999</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="41" t="s">
         <v>41</v>
       </c>
